--- a/artfynd/A 483-2025 artfynd.xlsx
+++ b/artfynd/A 483-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1907,6 +1907,126 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122494223</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56592</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Krogen NV 1270 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>554778</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6516095</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Hällmarker blandat med små skvattrampartier.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 483-2025 artfynd.xlsx
+++ b/artfynd/A 483-2025 artfynd.xlsx
@@ -1927,11 +1927,6 @@
       <c r="E13" t="n">
         <v>102613</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Orre</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Lyrurus tetrix</t>

--- a/artfynd/A 483-2025 artfynd.xlsx
+++ b/artfynd/A 483-2025 artfynd.xlsx
@@ -1912,7 +1912,7 @@
         <v>122494223</v>
       </c>
       <c r="B13" t="n">
-        <v>56592</v>
+        <v>56596</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1926,6 +1926,11 @@
       </c>
       <c r="E13" t="n">
         <v>102613</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>

--- a/artfynd/A 483-2025 artfynd.xlsx
+++ b/artfynd/A 483-2025 artfynd.xlsx
@@ -1912,7 +1912,7 @@
         <v>122494223</v>
       </c>
       <c r="B13" t="n">
-        <v>56596</v>
+        <v>56597</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 483-2025 artfynd.xlsx
+++ b/artfynd/A 483-2025 artfynd.xlsx
@@ -1912,7 +1912,7 @@
         <v>122494223</v>
       </c>
       <c r="B13" t="n">
-        <v>56597</v>
+        <v>56691</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 483-2025 artfynd.xlsx
+++ b/artfynd/A 483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679736</v>
       </c>
       <c r="B2" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113679737</v>
       </c>
       <c r="B3" t="n">
-        <v>78981</v>
+        <v>78983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113681109</v>
       </c>
       <c r="B4" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>113679734</v>
       </c>
       <c r="B5" t="n">
-        <v>78981</v>
+        <v>78983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>113679738</v>
       </c>
       <c r="B6" t="n">
-        <v>78981</v>
+        <v>78983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>113679735</v>
       </c>
       <c r="B7" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>113678161</v>
       </c>
       <c r="B12" t="n">
-        <v>96685</v>
+        <v>96688</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 483-2025 artfynd.xlsx
+++ b/artfynd/A 483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679736</v>
       </c>
       <c r="B2" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113679737</v>
       </c>
       <c r="B3" t="n">
-        <v>78983</v>
+        <v>78985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113681109</v>
       </c>
       <c r="B4" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>113679734</v>
       </c>
       <c r="B5" t="n">
-        <v>78983</v>
+        <v>78985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>113679738</v>
       </c>
       <c r="B6" t="n">
-        <v>78983</v>
+        <v>78985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>113679735</v>
       </c>
       <c r="B7" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>113678161</v>
       </c>
       <c r="B12" t="n">
-        <v>96688</v>
+        <v>96696</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 483-2025 artfynd.xlsx
+++ b/artfynd/A 483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679736</v>
       </c>
       <c r="B2" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113679737</v>
       </c>
       <c r="B3" t="n">
-        <v>78985</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113681109</v>
       </c>
       <c r="B4" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>113679734</v>
       </c>
       <c r="B5" t="n">
-        <v>78985</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>113679738</v>
       </c>
       <c r="B6" t="n">
-        <v>78985</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>113679735</v>
       </c>
       <c r="B7" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>113678161</v>
       </c>
       <c r="B12" t="n">
-        <v>96696</v>
+        <v>96706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 483-2025 artfynd.xlsx
+++ b/artfynd/A 483-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>113681109</v>
       </c>
       <c r="B4" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>113678161</v>
       </c>
       <c r="B12" t="n">
-        <v>96706</v>
+        <v>96707</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 483-2025 artfynd.xlsx
+++ b/artfynd/A 483-2025 artfynd.xlsx
@@ -1766,7 +1766,7 @@
         <v>113678161</v>
       </c>
       <c r="B12" t="n">
-        <v>96707</v>
+        <v>96708</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 483-2025 artfynd.xlsx
+++ b/artfynd/A 483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679736</v>
       </c>
       <c r="B2" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113679737</v>
       </c>
       <c r="B3" t="n">
-        <v>78993</v>
+        <v>78994</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113681109</v>
       </c>
       <c r="B4" t="n">
-        <v>93197</v>
+        <v>93198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>113679734</v>
       </c>
       <c r="B5" t="n">
-        <v>78993</v>
+        <v>78994</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>113679738</v>
       </c>
       <c r="B6" t="n">
-        <v>78993</v>
+        <v>78994</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>113679735</v>
       </c>
       <c r="B7" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>113678161</v>
       </c>
       <c r="B12" t="n">
-        <v>96708</v>
+        <v>96709</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 483-2025 artfynd.xlsx
+++ b/artfynd/A 483-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>113681109</v>
       </c>
       <c r="B4" t="n">
-        <v>93198</v>
+        <v>93200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>113678161</v>
       </c>
       <c r="B12" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 483-2025 artfynd.xlsx
+++ b/artfynd/A 483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679736</v>
       </c>
       <c r="B2" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113679737</v>
       </c>
       <c r="B3" t="n">
-        <v>78994</v>
+        <v>78995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113681109</v>
       </c>
       <c r="B4" t="n">
-        <v>93200</v>
+        <v>93201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>113679734</v>
       </c>
       <c r="B5" t="n">
-        <v>78994</v>
+        <v>78995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>113679738</v>
       </c>
       <c r="B6" t="n">
-        <v>78994</v>
+        <v>78995</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>113679735</v>
       </c>
       <c r="B7" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>113678161</v>
       </c>
       <c r="B12" t="n">
-        <v>96711</v>
+        <v>96712</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
